--- a/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,16; 81,82</t>
+          <t>57,26; 81,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,83; 81,18</t>
+          <t>61,74; 80,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,4; 79,23</t>
+          <t>62,92; 78,8</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,72; 78,79</t>
+          <t>61,66; 78,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,09; 82,65</t>
+          <t>70,9; 82,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,68; 79,0</t>
+          <t>67,87; 78,83</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,55; 78,47</t>
+          <t>67,37; 77,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,88; 78,66</t>
+          <t>69,64; 78,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,59; 76,84</t>
+          <t>69,65; 76,86</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,82; 78,59</t>
+          <t>69,01; 78,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,31; 79,52</t>
+          <t>50,01; 79,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,2; 77,27</t>
+          <t>60,03; 77,3</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,47; 84,49</t>
+          <t>75,53; 84,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,65; 79,83</t>
+          <t>72,59; 79,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,27; 80,69</t>
+          <t>75,26; 80,93</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,12; 83,67</t>
+          <t>74,59; 83,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,41; 97,53</t>
+          <t>82,57; 97,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80,7; 96,01</t>
+          <t>80,71; 95,48</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,96; 85,76</t>
+          <t>76,04; 86,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83,54; 89,54</t>
+          <t>83,52; 89,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,87; 87,17</t>
+          <t>81,92; 87,3</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>73,01; 77,81</t>
+          <t>72,76; 78,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>75,22; 85,5</t>
+          <t>75,24; 85,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75,22; 81,68</t>
+          <t>75,01; 81,51</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108974; 153310</t>
+          <t>107297; 153629</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97252; 127686</t>
+          <t>97112; 126996</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>218530; 273071</t>
+          <t>216859; 271584</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>115312; 147192</t>
+          <t>115198; 147324</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138767; 163637</t>
+          <t>140388; 163369</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>264286; 304014</t>
+          <t>261166; 303365</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>199523; 231782</t>
+          <t>198988; 230296</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>179854; 202443</t>
+          <t>179228; 201753</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>384675; 424707</t>
+          <t>385004; 424859</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>229757; 262372</t>
+          <t>230380; 262863</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>177172; 285756</t>
+          <t>179706; 284753</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>417293; 535601</t>
+          <t>416134; 535822</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>231771; 259456</t>
+          <t>231962; 258872</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>213713; 234825</t>
+          <t>213545; 234912</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>452596; 485171</t>
+          <t>452485; 486606</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>144186; 162766</t>
+          <t>145101; 163117</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>333930; 395187</t>
+          <t>334575; 396035</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>483961; 575828</t>
+          <t>484042; 572599</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>113959; 128659</t>
+          <t>114082; 129292</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>197497; 211667</t>
+          <t>197448; 211807</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>316361; 336855</t>
+          <t>316559; 337366</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1208325; 1287758</t>
+          <t>1204150; 1291266</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1434953; 1631081</t>
+          <t>1435429; 1623612</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2679933; 2910240</t>
+          <t>2672528; 2904034</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57,26; 81,99</t>
+          <t>62,6; 82,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,74; 80,74</t>
+          <t>63,98; 81,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,92; 78,8</t>
+          <t>66,21; 80,46</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,66; 78,86</t>
+          <t>60,99; 77,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,9; 82,51</t>
+          <t>71,26; 82,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,87; 78,83</t>
+          <t>67,98; 78,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,37; 77,97</t>
+          <t>68,65; 79,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,64; 78,39</t>
+          <t>69,62; 78,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,65; 76,86</t>
+          <t>70,43; 77,32</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,01; 78,74</t>
+          <t>69,28; 78,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,01; 79,24</t>
+          <t>74,71; 81,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,03; 77,3</t>
+          <t>73,07; 79,02</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,53; 84,3</t>
+          <t>75,65; 84,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,59; 79,86</t>
+          <t>72,44; 79,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,26; 80,93</t>
+          <t>75,51; 81,25</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,59; 83,85</t>
+          <t>75,05; 84,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,57; 97,74</t>
+          <t>79,77; 86,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80,71; 95,48</t>
+          <t>78,62; 84,13</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>76,04; 86,18</t>
+          <t>75,65; 85,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83,52; 89,6</t>
+          <t>83,2; 89,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,92; 87,3</t>
+          <t>81,43; 86,99</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>72,76; 78,02</t>
+          <t>73,32; 78,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>75,24; 85,1</t>
+          <t>76,73; 80,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75,01; 81,51</t>
+          <t>75,81; 78,55</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>133042</t>
+          <t>135942</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>113406</t>
+          <t>132918</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246447</t>
+          <t>268861</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>107297; 153629</t>
+          <t>115198; 152653</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97112; 126996</t>
+          <t>115931; 147080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>216859; 271584</t>
+          <t>241818; 293860</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>131708</t>
+          <t>149880</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>152658</t>
+          <t>173191</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284366</t>
+          <t>323071</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>115198; 147324</t>
+          <t>131834; 166841</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>140388; 163369</t>
+          <t>159491; 185299</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>261166; 303365</t>
+          <t>299077; 343177</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>215894</t>
+          <t>248529</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>191155</t>
+          <t>218770</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407049</t>
+          <t>467299</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>198988; 230296</t>
+          <t>231963; 266965</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>179228; 201753</t>
+          <t>204634; 230658</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>385004; 424859</t>
+          <t>444962; 488492</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>246856</t>
+          <t>259805</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>255331</t>
+          <t>276922</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>502188</t>
+          <t>536727</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>230380; 262863</t>
+          <t>243392; 276096</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>179706; 284753</t>
+          <t>264466; 289625</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>416134; 535822</t>
+          <t>515358; 557364</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>245795</t>
+          <t>267866</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>224672</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470466</t>
+          <t>517230</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>231962; 258872</t>
+          <t>252061; 281403</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>213545; 234912</t>
+          <t>236321; 260289</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>452485; 486606</t>
+          <t>497915; 535755</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>154712</t>
+          <t>171105</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>372236</t>
+          <t>184106</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>526948</t>
+          <t>355211</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>145101; 163117</t>
+          <t>161149; 181064</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>334575; 396035</t>
+          <t>176373; 191149</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>484042; 572599</t>
+          <t>342656; 366656</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>122062</t>
+          <t>132244</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>205124</t>
+          <t>221991</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>327187</t>
+          <t>354235</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>114082; 129292</t>
+          <t>123928; 139616</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>197448; 211807</t>
+          <t>213167; 229082</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>316559; 337366</t>
+          <t>342049; 365371</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1250069</t>
+          <t>1365372</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1514580</t>
+          <t>1457263</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2764650</t>
+          <t>2822634</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1204150; 1291266</t>
+          <t>1320587; 1407764</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1435429; 1623612</t>
+          <t>1424488; 1486307</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2672528; 2904034</t>
+          <t>2772875; 2873058</t>
         </is>
       </c>
     </row>
